--- a/src/test/resources/ImportTemplate/Validation.xlsx
+++ b/src/test/resources/ImportTemplate/Validation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A443C0-4530-4EB7-A975-C2A1031EC666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0834FA43-9171-4A19-A74E-1AF396C583D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
     <t>select * from public.customer</t>
   </si>
   <si>
-    <t>Validation_ImportSQL-DB-PostgreSQL--</t>
+    <t>Validation_ImportSQL-DB-PostgreSQL--Customer</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,8 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="41.28515625" customWidth="1"/>
+    <col min="1" max="1" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -401,7 +402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>

--- a/src/test/resources/ImportTemplate/Validation.xlsx
+++ b/src/test/resources/ImportTemplate/Validation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0834FA43-9171-4A19-A74E-1AF396C583D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F49400-546A-4E2B-A1AB-A06B3D5B5B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
     <t>select * from public.customer</t>
   </si>
   <si>
-    <t>Validation_ImportSQL-DB-PostgreSQL--Customer</t>
+    <t>Validation _ImportSQL DB PostgreSQL Customer</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Validation.xlsx
+++ b/src/test/resources/ImportTemplate/Validation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F49400-546A-4E2B-A1AB-A06B3D5B5B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF829E06-1559-4D5B-99BE-9FF2D9C90B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <t>select * from public.customer</t>
   </si>
   <si>
-    <t>Validation _ImportSQL DB PostgreSQL Customer</t>
+    <t>Validation_ImportSQL--DB-PostgreSQL_Customer</t>
   </si>
 </sst>
 </file>
@@ -60,9 +60,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
-      <color rgb="FF800000"/>
+      <color theme="1"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>

--- a/src/test/resources/ImportTemplate/Validation.xlsx
+++ b/src/test/resources/ImportTemplate/Validation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF829E06-1559-4D5B-99BE-9FF2D9C90B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEAF33C-2468-4ECB-9D9F-BB01BA7B7A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
     <t>select * from public.customer</t>
   </si>
   <si>
-    <t>Validation_ImportSQL--DB-PostgreSQL_Customer</t>
+    <t>Validation_ImportSQL__DB_PostgreSQL_Customer</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Validation.xlsx
+++ b/src/test/resources/ImportTemplate/Validation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEAF33C-2468-4ECB-9D9F-BB01BA7B7A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD82929-D411-488B-B7D1-073B1C531D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,10 +33,10 @@
     <t>sourceSql</t>
   </si>
   <si>
-    <t>select * from public.customer</t>
+    <t>Validation_ImportSQL__DB_PostgreSQL_Customer</t>
   </si>
   <si>
-    <t>Validation_ImportSQL__DB_PostgreSQL_Customer</t>
+    <t>select * from icedq.customer</t>
   </si>
 </sst>
 </file>
@@ -403,10 +403,10 @@
     </row>
     <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
